--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.30241803868292</v>
+        <v>10.28664293128597</v>
       </c>
       <c r="D2" t="n">
-        <v>62.98061428041271</v>
+        <v>10.23434982056706</v>
       </c>
       <c r="E2" t="n">
-        <v>11.87172569930263</v>
+        <v>1.929155426136677</v>
       </c>
       <c r="F2" t="n">
-        <v>11.94877971755492</v>
+        <v>1.941676704102674</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>85.25348194353636</v>
+        <v>13.85369081582466</v>
       </c>
       <c r="D3" t="n">
-        <v>85.25817536274137</v>
+        <v>13.85445349644547</v>
       </c>
       <c r="E3" t="n">
-        <v>11.87172569930263</v>
+        <v>1.929155426136677</v>
       </c>
       <c r="F3" t="n">
-        <v>11.94877971755492</v>
+        <v>1.941676704102674</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.18447128554747</v>
+        <v>8.642476583901464</v>
       </c>
       <c r="D4" t="n">
-        <v>53.06402712662869</v>
+        <v>8.622904408077163</v>
       </c>
       <c r="E4" t="n">
-        <v>11.87172569930263</v>
+        <v>1.929155426136677</v>
       </c>
       <c r="F4" t="n">
-        <v>11.94877971755492</v>
+        <v>1.941676704102674</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>73.15764504466031</v>
+        <v>11.8881173197573</v>
       </c>
       <c r="D5" t="n">
-        <v>73.14479463370664</v>
+        <v>11.88602912797733</v>
       </c>
       <c r="E5" t="n">
-        <v>11.87172569930263</v>
+        <v>1.929155426136677</v>
       </c>
       <c r="F5" t="n">
-        <v>11.94877971755492</v>
+        <v>1.941676704102674</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
